--- a/wiki/reports/daily/2026-09-29_일일보고.xlsx
+++ b/wiki/reports/daily/2026-09-29_일일보고.xlsx
@@ -76,7 +76,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +101,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -185,19 +190,25 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,10 +220,10 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -613,7 +624,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-09-29 08:04   |   전일: 9월 28일   |   월평균 기준: 이전 작업일 18일 평균   |   9월 누적 작업일: 19일</t>
+          <t>생성: 2026-09-29 16:00   |   전일: 9월 28일   |   월평균 기준: 이전 작업일 18일 평균   |   9월 누적 작업일: 19일</t>
         </is>
       </c>
     </row>
@@ -675,25 +686,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-39</v>
+        <v>-15</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.9512195121951219</v>
+        <v>-0.3658536585365854</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>29.8</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-27.77777777777778</v>
+        <v>-3.777777777777779</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-0.9328358208955224</v>
+        <v>-0.1268656716417911</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -704,29 +715,29 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>256</v>
+        <v>6454</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>8214</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-7958</v>
+        <v>-1760</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.9688336985634283</v>
+        <v>-0.2142683223764305</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>7476.9</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-7220.944444444444</v>
+        <v>-1022.944444444444</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-0.9657614147193223</v>
+        <v>-0.1368131664004161</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>0:04:16</t>
+          <t>1:47:34</t>
         </is>
       </c>
     </row>
@@ -737,25 +748,25 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>-46</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>-0.9583333333333334</v>
+      <c r="D6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>0.04166666666666666</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>-17.72222222222222</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>-0.8985915492957747</v>
+      <c r="G6" s="12" t="n">
+        <v>30.27777777777778</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>1.535211267605634</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
@@ -766,143 +777,143 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>628</v>
+        <v>17916</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>11177</v>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>-10549</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>-0.9438131877963676</v>
+      <c r="D7" s="12" t="n">
+        <v>6739</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>0.6029345978348394</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>7162.8</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>-6534.777777777777</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>-0.9123245171798651</v>
+      <c r="G7" s="12" t="n">
+        <v>10753.22222222222</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>1.501264251919646</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>0:10:28</t>
+          <t>4:58:36</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>합계  수량 (개)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>89</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-85</v>
+        <v>-13</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.9550561797752809</v>
+        <v>-0.1460674157303371</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>49.5</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>-45.5</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>-0.9191919191919192</v>
+      <c r="G8" s="12" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>0.5353535353535354</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>합계  가공시간 (초)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>884</v>
+        <v>24370</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>19391</v>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>-18507</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>-0.9544118405445825</v>
+      <c r="D9" s="12" t="n">
+        <v>4979</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>0.2567686039915424</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>14639.7</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>-13755.72222222222</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>-0.9396163406257708</v>
+      <c r="G9" s="12" t="n">
+        <v>9730.277777777777</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.6646490712103675</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>0:14:44</t>
+          <t>6:46:10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>합계  금액</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>89</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-85</v>
+        <v>-13</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.9550561797752809</v>
+        <v>-0.1460674157303371</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>48.8</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>-44.77777777777778</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>-0.9179954441913439</v>
+      <c r="G10" s="12" t="n">
+        <v>27.22222222222222</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>0.5580865603644647</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>9월 누적  (19일 / 29일 중 작업일)</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n">
-        <v>895</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>264399</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>882</v>
-      </c>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="16" t="n">
+        <v>967</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>287885</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>954</v>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -920,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -944,268 +955,1299 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>■ FAST GRIND</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>평</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="17" t="n">
+      <c r="C4" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>6_D5.1</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>0153</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr"/>
+      <c r="I4" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="21" t="n">
+        <v>256</v>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>0:04:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr"/>
+      <c r="I5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="K5" s="19" t="inlineStr">
+        <is>
+          <t>0:01:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>0202</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr"/>
+      <c r="I6" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>696</v>
+      </c>
+      <c r="K6" s="19" t="inlineStr">
+        <is>
+          <t>0:11:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>0202</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr"/>
+      <c r="I7" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>480</v>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>0:08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>614</v>
+      </c>
+      <c r="K8" s="19" t="inlineStr">
+        <is>
+          <t>0:10:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>0202 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="21" t="n">
+        <v>218</v>
+      </c>
+      <c r="K9" s="19" t="inlineStr">
+        <is>
+          <t>0:03:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>218</v>
+      </c>
+      <c r="K10" s="19" t="inlineStr">
+        <is>
+          <t>0:03:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H11" s="19" t="inlineStr"/>
+      <c r="I11" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>175</v>
+      </c>
+      <c r="K11" s="19" t="inlineStr">
+        <is>
+          <t>0:02:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>0104, 0168</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="inlineStr"/>
+      <c r="I12" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>525</v>
+      </c>
+      <c r="K12" s="19" t="inlineStr">
+        <is>
+          <t>0:08:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>R0.2_라핑</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="inlineStr"/>
+      <c r="I13" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>245</v>
+      </c>
+      <c r="K13" s="19" t="inlineStr">
+        <is>
+          <t>0:04:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H14" s="19" t="inlineStr"/>
+      <c r="I14" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="21" t="n">
+        <v>408</v>
+      </c>
+      <c r="K14" s="19" t="inlineStr">
+        <is>
+          <t>0:06:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>비</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>0153_D5.1</t>
-        </is>
-      </c>
-      <c r="H4" s="17" t="inlineStr"/>
-      <c r="I4" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="19" t="n">
-        <v>256</v>
-      </c>
-      <c r="K4" s="17" t="inlineStr">
-        <is>
-          <t>0:04:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="inlineStr"/>
+      <c r="I15" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>204</v>
+      </c>
+      <c r="K15" s="19" t="inlineStr">
+        <is>
+          <t>0:03:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="H16" s="19" t="inlineStr"/>
+      <c r="I16" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <v>2310</v>
+      </c>
+      <c r="K16" s="19" t="inlineStr">
+        <is>
+          <t>0:38:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>FAST GRIND 소계</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>256</v>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>0:04:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="J17" s="16" t="n">
+        <v>6454</v>
+      </c>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>1:47:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>■ GX7</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="J20" s="23" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="K20" s="23" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="22" t="n">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>볼</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="22" t="n">
+      <c r="C21" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E21" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>알파</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr"/>
-      <c r="H9" s="22" t="inlineStr"/>
-      <c r="I9" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="24" t="n">
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr"/>
+      <c r="I21" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="26" t="n">
         <v>628</v>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K21" s="24" t="inlineStr">
         <is>
           <t>0:10:28</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>NC_HSS</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr"/>
+      <c r="I22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="26" t="n">
+        <v>260</v>
+      </c>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>0:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>NC_HSS</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E23" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr"/>
+      <c r="I23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="26" t="n">
+        <v>360</v>
+      </c>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>0:06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="inlineStr">
+        <is>
+          <t>0202</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr"/>
+      <c r="I24" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="26" t="n">
+        <v>628</v>
+      </c>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>0:10:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G25" s="25" t="inlineStr">
+        <is>
+          <t>0202</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr"/>
+      <c r="I25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="26" t="n">
+        <v>415</v>
+      </c>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>0:06:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E26" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G26" s="25" t="inlineStr">
+        <is>
+          <t>0153</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr"/>
+      <c r="I26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="26" t="n">
+        <v>415</v>
+      </c>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>0:06:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E27" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G27" s="25" t="inlineStr">
+        <is>
+          <t>0171</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr"/>
+      <c r="I27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="26" t="n">
+        <v>771</v>
+      </c>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>0:12:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G28" s="25" t="inlineStr">
+        <is>
+          <t>0168, 0104 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr"/>
+      <c r="I28" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="26" t="n">
+        <v>470</v>
+      </c>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>0:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E29" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G29" s="25" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr"/>
+      <c r="I29" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" s="26" t="n">
+        <v>1388</v>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>0:23:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G30" s="25" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr"/>
+      <c r="I30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" s="26" t="n">
+        <v>1041</v>
+      </c>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>0:17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>평_라핑</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G31" s="25" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr"/>
+      <c r="I31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="26" t="n">
+        <v>1041</v>
+      </c>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>0:17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G32" s="25" t="inlineStr">
+        <is>
+          <t>0179</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr"/>
+      <c r="I32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" s="26" t="n">
+        <v>819</v>
+      </c>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>0:13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>R0.3_라핑</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F33" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G33" s="25" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr"/>
+      <c r="I33" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" s="26" t="n">
+        <v>550</v>
+      </c>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>0:09:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" s="25" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G34" s="25" t="inlineStr">
+        <is>
+          <t>0179</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr"/>
+      <c r="I34" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="J34" s="26" t="n">
+        <v>9130</v>
+      </c>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>2:32:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>GX7 소계</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>628</v>
-      </c>
-      <c r="K10" s="13" t="inlineStr">
-        <is>
-          <t>0:10:28</t>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="15" t="n"/>
+      <c r="I35" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="J35" s="16" t="n">
+        <v>17916</v>
+      </c>
+      <c r="K35" s="15" t="inlineStr">
+        <is>
+          <t>4:58:36</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A19:K19"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
